--- a/tasks/finalpool/scholarly-grant-proposal-prep/groundtruth_workspace/Grant_Prep.xlsx
+++ b/tasks/finalpool/scholarly-grant-proposal-prep/groundtruth_workspace/Grant_Prep.xlsx
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deep Learning for Medical Image Segmentation</t>
+          <t>Deep Learning for Medical Image Segmentation: A Comprehensive Review</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
